--- a/data/projects/56A0TXN/早期介入/交付预案/输出结果/计划表.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/输出结果/计划表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,38 +476,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>安装</t>
+          <t>L1机房准备</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>PMO</t>
-        </is>
-      </c>
+          <t>王长龙</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>已派发</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -523,45 +515,135 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>安装</t>
+          <t>机房改造实施</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
+          <t>王长龙</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>已派发</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>90</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>工程勘测</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>王长龙</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>安装</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>张三</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>PMO</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I5" t="n">
         <v>40</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
         </is>
